--- a/data/nelly_trends_monthly.xlsx
+++ b/data/nelly_trends_monthly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,16 +464,16 @@
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         <v>42429</v>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
         <v>77</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
@@ -498,16 +498,16 @@
         <v>42460</v>
       </c>
       <c r="B4" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" t="n">
         <v>82</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         <v>42490</v>
       </c>
       <c r="B5" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C5" t="n">
         <v>63</v>
@@ -524,7 +524,7 @@
         <v>87</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6">
@@ -535,10 +535,10 @@
         <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
@@ -549,13 +549,13 @@
         <v>42551</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
+        <v>71</v>
+      </c>
+      <c r="D7" t="n">
         <v>69</v>
-      </c>
-      <c r="D7" t="n">
-        <v>70</v>
       </c>
       <c r="E7" t="n">
         <v>77</v>
@@ -566,10 +566,10 @@
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" t="n">
         <v>55</v>
@@ -586,13 +586,13 @@
         <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
         <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -600,16 +600,16 @@
         <v>42643</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
         <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -617,16 +617,16 @@
         <v>42674</v>
       </c>
       <c r="B11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" t="n">
         <v>67</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -637,13 +637,13 @@
         <v>96</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
         <v>80</v>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -651,16 +651,16 @@
         <v>42735</v>
       </c>
       <c r="B13" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
@@ -668,13 +668,13 @@
         <v>42766</v>
       </c>
       <c r="B14" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" t="n">
         <v>60</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
         <v>74</v>
@@ -685,16 +685,16 @@
         <v>42794</v>
       </c>
       <c r="B15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" t="n">
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -702,16 +702,16 @@
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
         <v>74</v>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -719,16 +719,16 @@
         <v>42855</v>
       </c>
       <c r="B17" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>85</v>
       </c>
       <c r="E17" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -736,10 +736,10 @@
         <v>42886</v>
       </c>
       <c r="B18" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
         <v>74</v>
@@ -753,7 +753,7 @@
         <v>42916</v>
       </c>
       <c r="B19" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C19" t="n">
         <v>73</v>
@@ -762,7 +762,7 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -770,16 +770,16 @@
         <v>42947</v>
       </c>
       <c r="B20" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" t="n">
         <v>61</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
@@ -787,16 +787,16 @@
         <v>42978</v>
       </c>
       <c r="B21" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" t="n">
         <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
@@ -804,16 +804,16 @@
         <v>43008</v>
       </c>
       <c r="B22" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D22" t="n">
         <v>70</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -821,13 +821,13 @@
         <v>43039</v>
       </c>
       <c r="B23" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C23" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" t="n">
         <v>74</v>
@@ -838,16 +838,16 @@
         <v>43069</v>
       </c>
       <c r="B24" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C24" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D24" t="n">
         <v>89</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
@@ -855,16 +855,16 @@
         <v>43100</v>
       </c>
       <c r="B25" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D25" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
@@ -872,16 +872,16 @@
         <v>43131</v>
       </c>
       <c r="B26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" t="n">
         <v>55</v>
       </c>
       <c r="D26" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27">
@@ -892,7 +892,7 @@
         <v>58</v>
       </c>
       <c r="C27" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" t="n">
         <v>76</v>
@@ -906,16 +906,16 @@
         <v>43190</v>
       </c>
       <c r="B28" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C28" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D28" t="n">
         <v>90</v>
       </c>
       <c r="E28" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -926,13 +926,13 @@
         <v>76</v>
       </c>
       <c r="C29" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D29" t="n">
         <v>100</v>
       </c>
       <c r="E29" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30">
@@ -940,16 +940,16 @@
         <v>43251</v>
       </c>
       <c r="B30" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C30" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D30" t="n">
         <v>91</v>
       </c>
       <c r="E30" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
@@ -957,16 +957,16 @@
         <v>43281</v>
       </c>
       <c r="B31" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C31" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D31" t="n">
         <v>90</v>
       </c>
       <c r="E31" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32">
@@ -974,13 +974,13 @@
         <v>43312</v>
       </c>
       <c r="B32" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C32" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D32" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E32" t="n">
         <v>66</v>
@@ -991,7 +991,7 @@
         <v>43343</v>
       </c>
       <c r="B33" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" t="n">
         <v>53</v>
@@ -1000,7 +1000,7 @@
         <v>70</v>
       </c>
       <c r="E33" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
@@ -1008,10 +1008,10 @@
         <v>43373</v>
       </c>
       <c r="B34" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C34" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" t="n">
         <v>74</v>
@@ -1025,16 +1025,16 @@
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C35" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D35" t="n">
         <v>80</v>
       </c>
       <c r="E35" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
@@ -1042,16 +1042,16 @@
         <v>43434</v>
       </c>
       <c r="B36" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C36" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D36" t="n">
         <v>85</v>
       </c>
       <c r="E36" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
@@ -1062,7 +1062,7 @@
         <v>71</v>
       </c>
       <c r="C37" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D37" t="n">
         <v>79</v>
@@ -1076,16 +1076,16 @@
         <v>43496</v>
       </c>
       <c r="B38" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C38" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D38" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E38" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39">
@@ -1093,16 +1093,16 @@
         <v>43524</v>
       </c>
       <c r="B39" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C39" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D39" t="n">
         <v>75</v>
       </c>
       <c r="E39" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40">
@@ -1113,10 +1113,10 @@
         <v>69</v>
       </c>
       <c r="C40" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D40" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E40" t="n">
         <v>62</v>
@@ -1127,16 +1127,16 @@
         <v>43585</v>
       </c>
       <c r="B41" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C41" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D41" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E41" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42">
@@ -1144,16 +1144,16 @@
         <v>43616</v>
       </c>
       <c r="B42" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C42" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E42" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43">
@@ -1161,16 +1161,16 @@
         <v>43646</v>
       </c>
       <c r="B43" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C43" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D43" t="n">
         <v>81</v>
       </c>
       <c r="E43" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44">
@@ -1178,16 +1178,16 @@
         <v>43677</v>
       </c>
       <c r="B44" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C44" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D44" t="n">
         <v>58</v>
       </c>
       <c r="E44" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45">
@@ -1195,16 +1195,16 @@
         <v>43708</v>
       </c>
       <c r="B45" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C45" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D45" t="n">
         <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
@@ -1212,10 +1212,10 @@
         <v>43738</v>
       </c>
       <c r="B46" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C46" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D46" t="n">
         <v>63</v>
@@ -1229,13 +1229,13 @@
         <v>43769</v>
       </c>
       <c r="B47" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C47" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D47" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E47" t="n">
         <v>66</v>
@@ -1246,13 +1246,13 @@
         <v>43799</v>
       </c>
       <c r="B48" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C48" t="n">
         <v>100</v>
       </c>
       <c r="D48" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E48" t="n">
         <v>68</v>
@@ -1266,7 +1266,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D49" t="n">
         <v>75</v>
@@ -1283,7 +1283,7 @@
         <v>58</v>
       </c>
       <c r="C50" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D50" t="n">
         <v>63</v>
@@ -1297,16 +1297,16 @@
         <v>43890</v>
       </c>
       <c r="B51" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C51" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D51" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52">
@@ -1317,13 +1317,13 @@
         <v>60</v>
       </c>
       <c r="C52" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E52" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53">
@@ -1334,13 +1334,13 @@
         <v>60</v>
       </c>
       <c r="C53" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D53" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E53" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
@@ -1348,16 +1348,16 @@
         <v>43982</v>
       </c>
       <c r="B54" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C54" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D54" t="n">
         <v>62</v>
       </c>
       <c r="E54" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55">
@@ -1365,10 +1365,10 @@
         <v>44012</v>
       </c>
       <c r="B55" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C55" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D55" t="n">
         <v>66</v>
@@ -1382,10 +1382,10 @@
         <v>44043</v>
       </c>
       <c r="B56" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C56" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D56" t="n">
         <v>43</v>
@@ -1399,10 +1399,10 @@
         <v>44074</v>
       </c>
       <c r="B57" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C57" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D57" t="n">
         <v>47</v>
@@ -1416,10 +1416,10 @@
         <v>44104</v>
       </c>
       <c r="B58" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C58" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D58" t="n">
         <v>42</v>
@@ -1433,10 +1433,10 @@
         <v>44135</v>
       </c>
       <c r="B59" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C59" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D59" t="n">
         <v>42</v>
@@ -1453,13 +1453,13 @@
         <v>58</v>
       </c>
       <c r="C60" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D60" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E60" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61">
@@ -1467,16 +1467,16 @@
         <v>44196</v>
       </c>
       <c r="B61" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C61" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D61" t="n">
         <v>46</v>
       </c>
       <c r="E61" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62">
@@ -1484,13 +1484,13 @@
         <v>44227</v>
       </c>
       <c r="B62" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C62" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D62" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E62" t="n">
         <v>51</v>
@@ -1501,13 +1501,13 @@
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C63" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D63" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E63" t="n">
         <v>45</v>
@@ -1518,16 +1518,16 @@
         <v>44286</v>
       </c>
       <c r="B64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C64" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D64" t="n">
         <v>37</v>
       </c>
       <c r="E64" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
@@ -1535,13 +1535,13 @@
         <v>44316</v>
       </c>
       <c r="B65" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C65" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D65" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E65" t="n">
         <v>58</v>
@@ -1552,16 +1552,16 @@
         <v>44347</v>
       </c>
       <c r="B66" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C66" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D66" t="n">
         <v>42</v>
       </c>
       <c r="E66" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67">
@@ -1569,16 +1569,16 @@
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C67" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D67" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E67" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68">
@@ -1586,16 +1586,16 @@
         <v>44408</v>
       </c>
       <c r="B68" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C68" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D68" t="n">
         <v>29</v>
       </c>
       <c r="E68" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69">
@@ -1603,16 +1603,16 @@
         <v>44439</v>
       </c>
       <c r="B69" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C69" t="n">
         <v>49</v>
       </c>
       <c r="D69" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E69" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70">
@@ -1620,16 +1620,16 @@
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C70" t="n">
         <v>60</v>
       </c>
       <c r="D70" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E70" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
@@ -1637,16 +1637,16 @@
         <v>44500</v>
       </c>
       <c r="B71" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C71" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D71" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72">
@@ -1654,16 +1654,16 @@
         <v>44530</v>
       </c>
       <c r="B72" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C72" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D72" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E72" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73">
@@ -1671,16 +1671,16 @@
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C73" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D73" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E73" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74">
@@ -1688,16 +1688,16 @@
         <v>44592</v>
       </c>
       <c r="B74" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C74" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D74" t="n">
         <v>31</v>
       </c>
       <c r="E74" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75">
@@ -1705,13 +1705,13 @@
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C75" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D75" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E75" t="n">
         <v>51</v>
@@ -1725,7 +1725,7 @@
         <v>44</v>
       </c>
       <c r="C76" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D76" t="n">
         <v>42</v>
@@ -1739,16 +1739,16 @@
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C77" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D77" t="n">
         <v>45</v>
       </c>
       <c r="E77" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78">
@@ -1759,13 +1759,13 @@
         <v>49</v>
       </c>
       <c r="C78" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D78" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E78" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79">
@@ -1773,13 +1773,13 @@
         <v>44742</v>
       </c>
       <c r="B79" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C79" t="n">
         <v>53</v>
       </c>
       <c r="D79" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E79" t="n">
         <v>52</v>
@@ -1790,16 +1790,16 @@
         <v>44773</v>
       </c>
       <c r="B80" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C80" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D80" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E80" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81">
@@ -1816,7 +1816,7 @@
         <v>28</v>
       </c>
       <c r="E81" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82">
@@ -1824,16 +1824,16 @@
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C82" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D82" t="n">
         <v>29</v>
       </c>
       <c r="E82" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83">
@@ -1841,7 +1841,7 @@
         <v>44865</v>
       </c>
       <c r="B83" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C83" t="n">
         <v>51</v>
@@ -1850,7 +1850,7 @@
         <v>29</v>
       </c>
       <c r="E83" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84">
@@ -1858,16 +1858,16 @@
         <v>44895</v>
       </c>
       <c r="B84" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C84" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D84" t="n">
         <v>39</v>
       </c>
       <c r="E84" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85">
@@ -1881,7 +1881,7 @@
         <v>48</v>
       </c>
       <c r="D85" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E85" t="n">
         <v>41</v>
@@ -1892,16 +1892,16 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C86" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D86" t="n">
         <v>31</v>
       </c>
       <c r="E86" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87">
@@ -1912,10 +1912,10 @@
         <v>30</v>
       </c>
       <c r="C87" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D87" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E87" t="n">
         <v>38</v>
@@ -1926,16 +1926,16 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C88" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D88" t="n">
         <v>32</v>
       </c>
       <c r="E88" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89">
@@ -1943,10 +1943,10 @@
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C89" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D89" t="n">
         <v>39</v>
@@ -1960,13 +1960,13 @@
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C90" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D90" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E90" t="n">
         <v>44</v>
@@ -1980,7 +1980,7 @@
         <v>32</v>
       </c>
       <c r="C91" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D91" t="n">
         <v>28</v>
@@ -2003,7 +2003,7 @@
         <v>23</v>
       </c>
       <c r="E92" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93">
@@ -2011,10 +2011,10 @@
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C93" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D93" t="n">
         <v>24</v>
@@ -2028,16 +2028,16 @@
         <v>45199</v>
       </c>
       <c r="B94" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C94" t="n">
         <v>34</v>
       </c>
       <c r="D94" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E94" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95">
@@ -2054,7 +2054,7 @@
         <v>33</v>
       </c>
       <c r="E95" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96">
@@ -2062,7 +2062,7 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C96" t="n">
         <v>52</v>
@@ -2071,7 +2071,7 @@
         <v>40</v>
       </c>
       <c r="E96" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97">
@@ -2079,7 +2079,7 @@
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C97" t="n">
         <v>38</v>
@@ -2096,10 +2096,10 @@
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C98" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D98" t="n">
         <v>33</v>
@@ -2113,10 +2113,10 @@
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C99" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D99" t="n">
         <v>30</v>
@@ -2133,7 +2133,7 @@
         <v>30</v>
       </c>
       <c r="C100" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D100" t="n">
         <v>38</v>
@@ -2147,7 +2147,7 @@
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C101" t="n">
         <v>39</v>
@@ -2164,16 +2164,16 @@
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C102" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D102" t="n">
         <v>49</v>
       </c>
       <c r="E102" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="103">
@@ -2184,13 +2184,13 @@
         <v>34</v>
       </c>
       <c r="C103" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D103" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E103" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="104">
@@ -2198,7 +2198,7 @@
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C104" t="n">
         <v>33</v>
@@ -2207,7 +2207,7 @@
         <v>26</v>
       </c>
       <c r="E104" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105">
@@ -2215,7 +2215,7 @@
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C105" t="n">
         <v>36</v>
@@ -2224,7 +2224,7 @@
         <v>37</v>
       </c>
       <c r="E105" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106">
@@ -2232,10 +2232,10 @@
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C106" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D106" t="n">
         <v>46</v>
@@ -2249,13 +2249,13 @@
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C107" t="n">
         <v>45</v>
       </c>
       <c r="D107" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E107" t="n">
         <v>30</v>
@@ -2266,13 +2266,13 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C108" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D108" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E108" t="n">
         <v>35</v>
@@ -2283,13 +2283,13 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C109" t="n">
         <v>44</v>
       </c>
       <c r="D109" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E109" t="n">
         <v>27</v>
@@ -2303,10 +2303,10 @@
         <v>32</v>
       </c>
       <c r="C110" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D110" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E110" t="n">
         <v>32</v>
@@ -2337,10 +2337,10 @@
         <v>42</v>
       </c>
       <c r="C112" t="n">
+        <v>54</v>
+      </c>
+      <c r="D112" t="n">
         <v>53</v>
-      </c>
-      <c r="D112" t="n">
-        <v>52</v>
       </c>
       <c r="E112" t="n">
         <v>35</v>
@@ -2351,16 +2351,16 @@
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C113" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D113" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E113" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="114">
@@ -2368,13 +2368,13 @@
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C114" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D114" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E114" t="n">
         <v>38</v>
@@ -2385,10 +2385,10 @@
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C115" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D115" t="n">
         <v>42</v>
@@ -2402,13 +2402,13 @@
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C116" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D116" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E116" t="n">
         <v>34</v>
@@ -2419,16 +2419,16 @@
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C117" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D117" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E117" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="118">
@@ -2436,16 +2436,16 @@
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C118" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D118" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E118" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119">
@@ -2453,13 +2453,13 @@
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C119" t="n">
         <v>42</v>
       </c>
       <c r="D119" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E119" t="n">
         <v>33</v>
@@ -2470,16 +2470,16 @@
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C120" t="n">
         <v>60</v>
       </c>
       <c r="D120" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E120" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121">
@@ -2487,7 +2487,7 @@
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C121" t="n">
         <v>48</v>
@@ -2504,13 +2504,13 @@
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C122" t="n">
         <v>48</v>
       </c>
       <c r="D122" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E122" t="n">
         <v>33</v>
@@ -2521,16 +2521,33 @@
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C123" t="n">
         <v>41</v>
       </c>
       <c r="D123" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E123" t="n">
         <v>28</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B124" t="n">
+        <v>40</v>
+      </c>
+      <c r="C124" t="n">
+        <v>45</v>
+      </c>
+      <c r="D124" t="n">
+        <v>44</v>
+      </c>
+      <c r="E124" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/data/nelly_trends_monthly.xlsx
+++ b/data/nelly_trends_monthly.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,126 +421,126 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nelly_SE</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nelly_NO</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Nelly_DK</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Nelly_FI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>42429</v>
       </c>
       <c r="B3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C3" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D4" t="n">
         <v>82</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>42490</v>
       </c>
       <c r="B5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>42521</v>
       </c>
       <c r="B6" t="n">
         <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" t="n">
         <v>69</v>
@@ -562,48 +550,48 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>42613</v>
       </c>
       <c r="B9" t="n">
         <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D10" t="n">
         <v>59</v>
@@ -613,150 +601,150 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>42674</v>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" t="n">
+        <v>69</v>
+      </c>
+      <c r="E11" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>42704</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98</v>
+      </c>
+      <c r="C12" t="n">
+        <v>92</v>
+      </c>
+      <c r="D12" t="n">
+        <v>81</v>
+      </c>
+      <c r="E12" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>42735</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97</v>
+      </c>
+      <c r="C13" t="n">
+        <v>81</v>
+      </c>
+      <c r="D13" t="n">
+        <v>76</v>
+      </c>
+      <c r="E13" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>42766</v>
+      </c>
+      <c r="B14" t="n">
         <v>67</v>
       </c>
-      <c r="E11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>42704</v>
-      </c>
-      <c r="B12" t="n">
-        <v>96</v>
-      </c>
-      <c r="C12" t="n">
-        <v>95</v>
-      </c>
-      <c r="D12" t="n">
-        <v>80</v>
-      </c>
-      <c r="E12" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>42735</v>
-      </c>
-      <c r="B13" t="n">
-        <v>92</v>
-      </c>
-      <c r="C13" t="n">
-        <v>93</v>
-      </c>
-      <c r="D13" t="n">
-        <v>74</v>
-      </c>
-      <c r="E13" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>42766</v>
-      </c>
-      <c r="B14" t="n">
-        <v>68</v>
-      </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>42794</v>
       </c>
       <c r="B15" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
         <v>64</v>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>42855</v>
       </c>
       <c r="B17" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D17" t="n">
         <v>85</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>42886</v>
       </c>
       <c r="B18" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C18" t="n">
+        <v>72</v>
+      </c>
+      <c r="D18" t="n">
         <v>75</v>
       </c>
-      <c r="D18" t="n">
-        <v>74</v>
-      </c>
       <c r="E18" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>42916</v>
+      </c>
+      <c r="B19" t="n">
         <v>91</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>42916</v>
-      </c>
-      <c r="B19" t="n">
-        <v>88</v>
-      </c>
       <c r="C19" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D19" t="n">
         <v>71</v>
@@ -766,235 +754,235 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>42947</v>
       </c>
       <c r="B20" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="B21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E21" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B22" t="n">
+        <v>77</v>
+      </c>
+      <c r="C22" t="n">
+        <v>64</v>
+      </c>
+      <c r="D22" t="n">
         <v>71</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>43039</v>
+      </c>
+      <c r="B23" t="n">
+        <v>76</v>
+      </c>
+      <c r="C23" t="n">
         <v>67</v>
-      </c>
-      <c r="D22" t="n">
-        <v>70</v>
-      </c>
-      <c r="E22" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>43039</v>
-      </c>
-      <c r="B23" t="n">
-        <v>73</v>
-      </c>
-      <c r="C23" t="n">
-        <v>70</v>
       </c>
       <c r="D23" t="n">
         <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>43069</v>
       </c>
       <c r="B24" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C24" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D24" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B25" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C25" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E25" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>43131</v>
+      </c>
+      <c r="B26" t="n">
+        <v>63</v>
+      </c>
+      <c r="C26" t="n">
+        <v>53</v>
+      </c>
+      <c r="D26" t="n">
+        <v>73</v>
+      </c>
+      <c r="E26" t="n">
         <v>65</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>43131</v>
-      </c>
-      <c r="B26" t="n">
-        <v>59</v>
-      </c>
-      <c r="C26" t="n">
-        <v>55</v>
-      </c>
-      <c r="D26" t="n">
-        <v>72</v>
-      </c>
-      <c r="E26" t="n">
-        <v>66</v>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>43159</v>
       </c>
       <c r="B27" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C27" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D27" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E27" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B28" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C28" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D28" t="n">
         <v>90</v>
       </c>
       <c r="E28" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C29" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D29" t="n">
         <v>100</v>
       </c>
       <c r="E29" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="B30" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C30" t="n">
+        <v>68</v>
+      </c>
+      <c r="D30" t="n">
+        <v>93</v>
+      </c>
+      <c r="E30" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>43281</v>
+      </c>
+      <c r="B31" t="n">
+        <v>77</v>
+      </c>
+      <c r="C31" t="n">
+        <v>66</v>
+      </c>
+      <c r="D31" t="n">
+        <v>91</v>
+      </c>
+      <c r="E31" t="n">
         <v>70</v>
       </c>
-      <c r="D30" t="n">
-        <v>91</v>
-      </c>
-      <c r="E30" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>43281</v>
-      </c>
-      <c r="B31" t="n">
-        <v>73</v>
-      </c>
-      <c r="C31" t="n">
-        <v>70</v>
-      </c>
-      <c r="D31" t="n">
-        <v>90</v>
-      </c>
-      <c r="E31" t="n">
-        <v>71</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="B32" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C32" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D32" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E32" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C33" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" t="n">
         <v>70</v>
@@ -1004,14 +992,14 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B34" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C34" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D34" t="n">
         <v>74</v>
@@ -1021,48 +1009,48 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C35" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D35" t="n">
         <v>80</v>
       </c>
       <c r="E35" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B36" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C36" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D36" t="n">
         <v>85</v>
       </c>
       <c r="E36" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>43465</v>
+      </c>
+      <c r="B37" t="n">
         <v>74</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>43465</v>
-      </c>
-      <c r="B37" t="n">
+      <c r="C37" t="n">
         <v>71</v>
-      </c>
-      <c r="C37" t="n">
-        <v>74</v>
       </c>
       <c r="D37" t="n">
         <v>79</v>
@@ -1072,82 +1060,82 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B38" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C38" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D38" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E38" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B39" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C39" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D39" t="n">
         <v>75</v>
       </c>
       <c r="E39" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>43555</v>
+      </c>
+      <c r="B40" t="n">
+        <v>72</v>
+      </c>
+      <c r="C40" t="n">
         <v>62</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>43555</v>
-      </c>
-      <c r="B40" t="n">
-        <v>69</v>
-      </c>
-      <c r="C40" t="n">
-        <v>65</v>
-      </c>
       <c r="D40" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E40" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B41" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D41" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E41" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B42" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C42" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D42" t="n">
         <v>77</v>
@@ -1157,65 +1145,65 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B43" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C43" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E43" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>43677</v>
       </c>
       <c r="B44" t="n">
         <v>65</v>
       </c>
       <c r="C44" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D44" t="n">
         <v>58</v>
       </c>
       <c r="E44" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43708</v>
+      </c>
+      <c r="B45" t="n">
         <v>61</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>43708</v>
-      </c>
-      <c r="B45" t="n">
-        <v>58</v>
-      </c>
       <c r="C45" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B46" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C46" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D46" t="n">
         <v>63</v>
@@ -1225,11 +1213,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B47" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C47" t="n">
         <v>72</v>
@@ -1242,184 +1230,184 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B48" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C48" t="n">
         <v>100</v>
       </c>
       <c r="D48" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E48" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B49" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C49" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D49" t="n">
         <v>75</v>
       </c>
       <c r="E49" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C50" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D50" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E50" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B51" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C51" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D51" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E51" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B52" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C52" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D52" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B53" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C53" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D53" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B54" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D54" t="n">
         <v>62</v>
       </c>
       <c r="E54" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B55" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C55" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D55" t="n">
         <v>66</v>
       </c>
       <c r="E55" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B56" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C56" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D56" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E56" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B57" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C57" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D57" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E57" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B58" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C58" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D58" t="n">
         <v>42</v>
@@ -1429,31 +1417,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B59" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C59" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D59" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E59" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B60" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C60" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D60" t="n">
         <v>49</v>
@@ -1463,303 +1451,303 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B61" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C61" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D61" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E61" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B62" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C62" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D62" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E62" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C63" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D63" t="n">
+        <v>37</v>
+      </c>
+      <c r="E63" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>44286</v>
+      </c>
+      <c r="B64" t="n">
         <v>36</v>
       </c>
-      <c r="E63" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>44286</v>
-      </c>
-      <c r="B64" t="n">
-        <v>41</v>
-      </c>
       <c r="C64" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D64" t="n">
         <v>37</v>
       </c>
       <c r="E64" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B65" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C65" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D65" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E65" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B66" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C66" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D66" t="n">
         <v>42</v>
       </c>
       <c r="E66" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C67" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D67" t="n">
         <v>44</v>
       </c>
       <c r="E67" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B68" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C68" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D68" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E68" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B69" t="n">
+        <v>40</v>
+      </c>
+      <c r="C69" t="n">
+        <v>47</v>
+      </c>
+      <c r="D69" t="n">
         <v>38</v>
-      </c>
-      <c r="C69" t="n">
-        <v>49</v>
-      </c>
-      <c r="D69" t="n">
-        <v>36</v>
       </c>
       <c r="E69" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B70" t="n">
         <v>54</v>
       </c>
       <c r="C70" t="n">
+        <v>58</v>
+      </c>
+      <c r="D70" t="n">
+        <v>36</v>
+      </c>
+      <c r="E70" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="B71" t="n">
+        <v>48</v>
+      </c>
+      <c r="C71" t="n">
+        <v>55</v>
+      </c>
+      <c r="D71" t="n">
+        <v>43</v>
+      </c>
+      <c r="E71" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="B72" t="n">
         <v>60</v>
       </c>
-      <c r="D70" t="n">
-        <v>35</v>
-      </c>
-      <c r="E70" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>44500</v>
-      </c>
-      <c r="B71" t="n">
-        <v>45</v>
-      </c>
-      <c r="C71" t="n">
-        <v>59</v>
-      </c>
-      <c r="D71" t="n">
-        <v>42</v>
-      </c>
-      <c r="E71" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>44530</v>
-      </c>
-      <c r="B72" t="n">
-        <v>59</v>
-      </c>
       <c r="C72" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D72" t="n">
         <v>48</v>
       </c>
       <c r="E72" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C73" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D73" t="n">
         <v>43</v>
       </c>
       <c r="E73" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B74" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C74" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D74" t="n">
         <v>31</v>
       </c>
       <c r="E74" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C75" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D75" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E75" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B76" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C76" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D76" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E76" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C77" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D77" t="n">
         <v>45</v>
       </c>
       <c r="E77" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B78" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C78" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D78" t="n">
         <v>42</v>
@@ -1769,65 +1757,65 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B79" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C79" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D79" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E79" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B80" t="n">
         <v>31</v>
       </c>
       <c r="C80" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E80" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B81" t="n">
         <v>32</v>
       </c>
       <c r="C81" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D81" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E81" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C82" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D82" t="n">
         <v>29</v>
@@ -1837,150 +1825,150 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B83" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C83" t="n">
+        <v>49</v>
+      </c>
+      <c r="D83" t="n">
+        <v>30</v>
+      </c>
+      <c r="E83" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B84" t="n">
         <v>51</v>
       </c>
-      <c r="D83" t="n">
-        <v>29</v>
-      </c>
-      <c r="E83" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>44895</v>
-      </c>
-      <c r="B84" t="n">
-        <v>45</v>
-      </c>
       <c r="C84" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D84" t="n">
         <v>39</v>
       </c>
       <c r="E84" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B85" t="n">
         <v>37</v>
       </c>
       <c r="C85" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D85" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E85" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C86" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D86" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E86" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B87" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C87" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E87" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C88" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D88" t="n">
         <v>32</v>
       </c>
       <c r="E88" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C89" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D89" t="n">
         <v>39</v>
       </c>
       <c r="E89" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C90" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D90" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E90" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B91" t="n">
         <v>32</v>
       </c>
       <c r="C91" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D91" t="n">
         <v>28</v>
@@ -1990,31 +1978,31 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C92" t="n">
         <v>26</v>
       </c>
       <c r="D92" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E92" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C93" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D93" t="n">
         <v>24</v>
@@ -2024,14 +2012,14 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B94" t="n">
         <v>29</v>
       </c>
       <c r="C94" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D94" t="n">
         <v>31</v>
@@ -2041,65 +2029,65 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C95" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D95" t="n">
         <v>33</v>
       </c>
       <c r="E95" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C96" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D96" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E96" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C97" t="n">
+        <v>37</v>
+      </c>
+      <c r="D97" t="n">
         <v>38</v>
-      </c>
-      <c r="D97" t="n">
-        <v>37</v>
       </c>
       <c r="E97" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C98" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D98" t="n">
         <v>33</v>
@@ -2109,48 +2097,48 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C99" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D99" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E99" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C100" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D100" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E100" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C101" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D101" t="n">
         <v>43</v>
@@ -2160,48 +2148,48 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B102" t="n">
         <v>43</v>
       </c>
       <c r="C102" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D102" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E102" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C103" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D103" t="n">
         <v>41</v>
       </c>
       <c r="E103" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C104" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D104" t="n">
         <v>26</v>
@@ -2211,116 +2199,116 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C105" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D105" t="n">
         <v>37</v>
       </c>
       <c r="E105" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C106" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D106" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E106" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C107" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D107" t="n">
         <v>54</v>
       </c>
       <c r="E107" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B108" t="n">
         <v>40</v>
       </c>
       <c r="C108" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D108" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E108" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B109" t="n">
         <v>37</v>
       </c>
       <c r="C109" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D109" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E109" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C110" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D110" t="n">
         <v>51</v>
       </c>
       <c r="E110" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C111" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D111" t="n">
         <v>45</v>
@@ -2330,14 +2318,14 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C112" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D112" t="n">
         <v>53</v>
@@ -2347,31 +2335,31 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C113" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D113" t="n">
         <v>51</v>
       </c>
       <c r="E113" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C114" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D114" t="n">
         <v>52</v>
@@ -2381,65 +2369,65 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C115" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D115" t="n">
         <v>42</v>
       </c>
       <c r="E115" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C116" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D116" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E116" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B117" t="n">
+        <v>37</v>
+      </c>
+      <c r="C117" t="n">
+        <v>54</v>
+      </c>
+      <c r="D117" t="n">
+        <v>53</v>
+      </c>
+      <c r="E117" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B118" t="n">
         <v>35</v>
       </c>
-      <c r="C117" t="n">
-        <v>56</v>
-      </c>
-      <c r="D117" t="n">
-        <v>51</v>
-      </c>
-      <c r="E117" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>45930</v>
-      </c>
-      <c r="B118" t="n">
-        <v>34</v>
-      </c>
       <c r="C118" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D118" t="n">
         <v>44</v>
@@ -2449,14 +2437,14 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C119" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D119" t="n">
         <v>51</v>
@@ -2466,31 +2454,31 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C120" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D120" t="n">
         <v>56</v>
       </c>
       <c r="E120" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C121" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D121" t="n">
         <v>44</v>
@@ -2500,31 +2488,31 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C122" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D122" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E122" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C123" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D123" t="n">
         <v>33</v>
@@ -2534,17 +2522,17 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C124" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D124" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E124" t="n">
         <v>35</v>

--- a/data/nelly_trends_monthly.xlsx
+++ b/data/nelly_trends_monthly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>42429</v>
       </c>
       <c r="B3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
         <v>51</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E3" t="n">
         <v>85</v>
@@ -486,13 +486,13 @@
         <v>42460</v>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="n">
         <v>83</v>
@@ -503,7 +503,7 @@
         <v>42490</v>
       </c>
       <c r="B5" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C5" t="n">
         <v>62</v>
@@ -512,7 +512,7 @@
         <v>88</v>
       </c>
       <c r="E5" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +523,7 @@
         <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" t="n">
         <v>82</v>
@@ -537,13 +537,13 @@
         <v>42551</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
         <v>77</v>
@@ -554,13 +554,13 @@
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
         <v>53</v>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
         <v>71</v>
@@ -571,7 +571,7 @@
         <v>42613</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
         <v>51</v>
@@ -580,7 +580,7 @@
         <v>51</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -588,16 +588,16 @@
         <v>42643</v>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" t="n">
         <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -605,16 +605,16 @@
         <v>42674</v>
       </c>
       <c r="B11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" t="n">
         <v>69</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -625,13 +625,13 @@
         <v>98</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
         <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -639,16 +639,16 @@
         <v>42735</v>
       </c>
       <c r="B13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
@@ -656,16 +656,16 @@
         <v>42766</v>
       </c>
       <c r="B14" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C14" t="n">
         <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -673,16 +673,16 @@
         <v>42794</v>
       </c>
       <c r="B15" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>64</v>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
@@ -690,16 +690,16 @@
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C16" t="n">
         <v>61</v>
       </c>
       <c r="D16" t="n">
+        <v>76</v>
+      </c>
+      <c r="E16" t="n">
         <v>75</v>
-      </c>
-      <c r="E16" t="n">
-        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -707,16 +707,16 @@
         <v>42855</v>
       </c>
       <c r="B17" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E17" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -724,16 +724,16 @@
         <v>42886</v>
       </c>
       <c r="B18" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C18" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
         <v>75</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -741,13 +741,13 @@
         <v>42916</v>
       </c>
       <c r="B19" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C19" t="n">
         <v>71</v>
       </c>
       <c r="D19" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" t="n">
         <v>71</v>
@@ -758,16 +758,16 @@
         <v>42947</v>
       </c>
       <c r="B20" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21">
@@ -775,13 +775,13 @@
         <v>42978</v>
       </c>
       <c r="B21" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
         <v>59</v>
@@ -809,16 +809,16 @@
         <v>43039</v>
       </c>
       <c r="B23" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C23" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D23" t="n">
         <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
@@ -826,16 +826,16 @@
         <v>43069</v>
       </c>
       <c r="B24" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C24" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D24" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E24" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
@@ -843,16 +843,16 @@
         <v>43100</v>
       </c>
       <c r="B25" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C25" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
@@ -860,13 +860,13 @@
         <v>43131</v>
       </c>
       <c r="B26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" t="n">
         <v>53</v>
       </c>
       <c r="D26" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E26" t="n">
         <v>65</v>
@@ -877,16 +877,16 @@
         <v>43159</v>
       </c>
       <c r="B27" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" t="n">
         <v>51</v>
       </c>
       <c r="D27" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E27" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
@@ -894,7 +894,7 @@
         <v>43190</v>
       </c>
       <c r="B28" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" t="n">
         <v>49</v>
@@ -903,7 +903,7 @@
         <v>90</v>
       </c>
       <c r="E28" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -911,7 +911,7 @@
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" t="n">
         <v>61</v>
@@ -920,7 +920,7 @@
         <v>100</v>
       </c>
       <c r="E29" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30">
@@ -928,16 +928,16 @@
         <v>43251</v>
       </c>
       <c r="B30" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C30" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D30" t="n">
         <v>93</v>
       </c>
       <c r="E30" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
@@ -962,10 +962,10 @@
         <v>43312</v>
       </c>
       <c r="B32" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D32" t="n">
         <v>74</v>
@@ -979,16 +979,16 @@
         <v>43343</v>
       </c>
       <c r="B33" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C33" t="n">
         <v>52</v>
       </c>
       <c r="D33" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         <v>43373</v>
       </c>
       <c r="B34" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C34" t="n">
         <v>65</v>
@@ -1005,7 +1005,7 @@
         <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35">
@@ -1013,13 +1013,13 @@
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C35" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D35" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E35" t="n">
         <v>68</v>
@@ -1033,10 +1033,10 @@
         <v>77</v>
       </c>
       <c r="C36" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D36" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E36" t="n">
         <v>72</v>
@@ -1047,13 +1047,13 @@
         <v>43465</v>
       </c>
       <c r="B37" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C37" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D37" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E37" t="n">
         <v>59</v>
@@ -1064,16 +1064,16 @@
         <v>43496</v>
       </c>
       <c r="B38" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D38" t="n">
         <v>76</v>
       </c>
       <c r="E38" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39">
@@ -1084,13 +1084,13 @@
         <v>67</v>
       </c>
       <c r="C39" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E39" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40">
@@ -1104,10 +1104,10 @@
         <v>62</v>
       </c>
       <c r="D40" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E40" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41">
@@ -1118,13 +1118,13 @@
         <v>80</v>
       </c>
       <c r="C41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D41" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E41" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42">
@@ -1132,10 +1132,10 @@
         <v>43616</v>
       </c>
       <c r="B42" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C42" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D42" t="n">
         <v>77</v>
@@ -1149,16 +1149,16 @@
         <v>43646</v>
       </c>
       <c r="B43" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C43" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D43" t="n">
         <v>82</v>
       </c>
       <c r="E43" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
@@ -1166,16 +1166,16 @@
         <v>43677</v>
       </c>
       <c r="B44" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C44" t="n">
         <v>60</v>
       </c>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45">
@@ -1183,16 +1183,16 @@
         <v>43708</v>
       </c>
       <c r="B45" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C45" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D45" t="n">
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
@@ -1200,16 +1200,16 @@
         <v>43738</v>
       </c>
       <c r="B46" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C46" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D46" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E46" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47">
@@ -1217,13 +1217,13 @@
         <v>43769</v>
       </c>
       <c r="B47" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C47" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D47" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E47" t="n">
         <v>66</v>
@@ -1234,16 +1234,16 @@
         <v>43799</v>
       </c>
       <c r="B48" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C48" t="n">
         <v>100</v>
       </c>
       <c r="D48" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E48" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49">
@@ -1251,16 +1251,16 @@
         <v>43830</v>
       </c>
       <c r="B49" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C49" t="n">
         <v>77</v>
       </c>
       <c r="D49" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E49" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50">
@@ -1268,10 +1268,10 @@
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C50" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D50" t="n">
         <v>64</v>
@@ -1288,13 +1288,13 @@
         <v>60</v>
       </c>
       <c r="C51" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D51" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E51" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52">
@@ -1302,16 +1302,16 @@
         <v>43921</v>
       </c>
       <c r="B52" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53">
@@ -1319,16 +1319,16 @@
         <v>43951</v>
       </c>
       <c r="B53" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C53" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D53" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E53" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
@@ -1336,13 +1336,13 @@
         <v>43982</v>
       </c>
       <c r="B54" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C54" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D54" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E54" t="n">
         <v>71</v>
@@ -1353,10 +1353,10 @@
         <v>44012</v>
       </c>
       <c r="B55" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C55" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D55" t="n">
         <v>66</v>
@@ -1373,13 +1373,13 @@
         <v>51</v>
       </c>
       <c r="C56" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D56" t="n">
         <v>44</v>
       </c>
       <c r="E56" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57">
@@ -1390,13 +1390,13 @@
         <v>54</v>
       </c>
       <c r="C57" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D57" t="n">
         <v>48</v>
       </c>
       <c r="E57" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58">
@@ -1404,13 +1404,13 @@
         <v>44104</v>
       </c>
       <c r="B58" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C58" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D58" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E58" t="n">
         <v>56</v>
@@ -1424,13 +1424,13 @@
         <v>64</v>
       </c>
       <c r="C59" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D59" t="n">
         <v>43</v>
       </c>
       <c r="E59" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60">
@@ -1441,10 +1441,10 @@
         <v>62</v>
       </c>
       <c r="C60" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D60" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E60" t="n">
         <v>62</v>
@@ -1455,10 +1455,10 @@
         <v>44196</v>
       </c>
       <c r="B61" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C61" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D61" t="n">
         <v>47</v>
@@ -1472,7 +1472,7 @@
         <v>44227</v>
       </c>
       <c r="B62" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C62" t="n">
         <v>44</v>
@@ -1498,7 +1498,7 @@
         <v>37</v>
       </c>
       <c r="E63" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
@@ -1506,7 +1506,7 @@
         <v>44286</v>
       </c>
       <c r="B64" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C64" t="n">
         <v>50</v>
@@ -1526,13 +1526,13 @@
         <v>45</v>
       </c>
       <c r="C65" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D65" t="n">
         <v>40</v>
       </c>
       <c r="E65" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66">
@@ -1540,7 +1540,7 @@
         <v>44347</v>
       </c>
       <c r="B66" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C66" t="n">
         <v>53</v>
@@ -1549,7 +1549,7 @@
         <v>42</v>
       </c>
       <c r="E66" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67">
@@ -1557,13 +1557,13 @@
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C67" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D67" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E67" t="n">
         <v>62</v>
@@ -1591,7 +1591,7 @@
         <v>44439</v>
       </c>
       <c r="B69" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C69" t="n">
         <v>47</v>
@@ -1608,10 +1608,10 @@
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C70" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D70" t="n">
         <v>36</v>
@@ -1625,10 +1625,10 @@
         <v>44500</v>
       </c>
       <c r="B71" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C71" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D71" t="n">
         <v>43</v>
@@ -1642,16 +1642,16 @@
         <v>44530</v>
       </c>
       <c r="B72" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C72" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D72" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E72" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73">
@@ -1659,16 +1659,16 @@
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C73" t="n">
         <v>66</v>
       </c>
       <c r="D73" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E73" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74">
@@ -1676,16 +1676,16 @@
         <v>44592</v>
       </c>
       <c r="B74" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C74" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D74" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E74" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75">
@@ -1699,7 +1699,7 @@
         <v>52</v>
       </c>
       <c r="D75" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E75" t="n">
         <v>51</v>
@@ -1710,7 +1710,7 @@
         <v>44651</v>
       </c>
       <c r="B76" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C76" t="n">
         <v>48</v>
@@ -1719,7 +1719,7 @@
         <v>43</v>
       </c>
       <c r="E76" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77">
@@ -1727,10 +1727,10 @@
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C77" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D77" t="n">
         <v>45</v>
@@ -1744,16 +1744,16 @@
         <v>44712</v>
       </c>
       <c r="B78" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C78" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D78" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E78" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79">
@@ -1761,13 +1761,13 @@
         <v>44742</v>
       </c>
       <c r="B79" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C79" t="n">
         <v>51</v>
       </c>
       <c r="D79" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E79" t="n">
         <v>52</v>
@@ -1778,13 +1778,13 @@
         <v>44773</v>
       </c>
       <c r="B80" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C80" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D80" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E80" t="n">
         <v>47</v>
@@ -1798,10 +1798,10 @@
         <v>32</v>
       </c>
       <c r="C81" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D81" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E81" t="n">
         <v>47</v>
@@ -1812,13 +1812,13 @@
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C82" t="n">
         <v>45</v>
       </c>
       <c r="D82" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E82" t="n">
         <v>49</v>
@@ -1829,13 +1829,13 @@
         <v>44865</v>
       </c>
       <c r="B83" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C83" t="n">
         <v>49</v>
       </c>
       <c r="D83" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E83" t="n">
         <v>46</v>
@@ -1846,10 +1846,10 @@
         <v>44895</v>
       </c>
       <c r="B84" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C84" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D84" t="n">
         <v>39</v>
@@ -1869,7 +1869,7 @@
         <v>46</v>
       </c>
       <c r="D85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E85" t="n">
         <v>41</v>
@@ -1880,7 +1880,7 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C86" t="n">
         <v>42</v>
@@ -1889,7 +1889,7 @@
         <v>32</v>
       </c>
       <c r="E86" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87">
@@ -1897,7 +1897,7 @@
         <v>44985</v>
       </c>
       <c r="B87" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C87" t="n">
         <v>36</v>
@@ -1914,16 +1914,16 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C88" t="n">
         <v>35</v>
       </c>
       <c r="D88" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E88" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89">
@@ -1931,16 +1931,16 @@
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C89" t="n">
         <v>35</v>
       </c>
       <c r="D89" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E89" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90">
@@ -1948,13 +1948,13 @@
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C90" t="n">
         <v>41</v>
       </c>
       <c r="D90" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E90" t="n">
         <v>44</v>
@@ -1965,13 +1965,13 @@
         <v>45107</v>
       </c>
       <c r="B91" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C91" t="n">
         <v>37</v>
       </c>
       <c r="D91" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E91" t="n">
         <v>39</v>
@@ -1982,10 +1982,10 @@
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C92" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D92" t="n">
         <v>24</v>
@@ -2008,7 +2008,7 @@
         <v>24</v>
       </c>
       <c r="E93" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94">
@@ -2016,7 +2016,7 @@
         <v>45199</v>
       </c>
       <c r="B94" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C94" t="n">
         <v>33</v>
@@ -2025,7 +2025,7 @@
         <v>31</v>
       </c>
       <c r="E94" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95">
@@ -2033,13 +2033,13 @@
         <v>45230</v>
       </c>
       <c r="B95" t="n">
+        <v>36</v>
+      </c>
+      <c r="C95" t="n">
         <v>34</v>
       </c>
-      <c r="C95" t="n">
-        <v>33</v>
-      </c>
       <c r="D95" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E95" t="n">
         <v>30</v>
@@ -2050,16 +2050,16 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C96" t="n">
         <v>50</v>
       </c>
       <c r="D96" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E96" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="97">
@@ -2067,13 +2067,13 @@
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C97" t="n">
+        <v>35</v>
+      </c>
+      <c r="D97" t="n">
         <v>37</v>
-      </c>
-      <c r="D97" t="n">
-        <v>38</v>
       </c>
       <c r="E97" t="n">
         <v>24</v>
@@ -2101,10 +2101,10 @@
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C99" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D99" t="n">
         <v>31</v>
@@ -2118,10 +2118,10 @@
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C100" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D100" t="n">
         <v>39</v>
@@ -2135,16 +2135,16 @@
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C101" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D101" t="n">
         <v>43</v>
       </c>
       <c r="E101" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102">
@@ -2152,13 +2152,13 @@
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C102" t="n">
         <v>44</v>
       </c>
       <c r="D102" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E102" t="n">
         <v>43</v>
@@ -2169,7 +2169,7 @@
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C103" t="n">
         <v>38</v>
@@ -2186,7 +2186,7 @@
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C104" t="n">
         <v>32</v>
@@ -2195,7 +2195,7 @@
         <v>26</v>
       </c>
       <c r="E104" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105">
@@ -2220,16 +2220,16 @@
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C106" t="n">
         <v>40</v>
       </c>
       <c r="D106" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E106" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107">
@@ -2237,13 +2237,13 @@
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C107" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D107" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E107" t="n">
         <v>29</v>
@@ -2254,13 +2254,13 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C108" t="n">
         <v>58</v>
       </c>
       <c r="D108" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E108" t="n">
         <v>35</v>
@@ -2271,16 +2271,16 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C109" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D109" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E109" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110">
@@ -2288,7 +2288,7 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C110" t="n">
         <v>45</v>
@@ -2308,10 +2308,10 @@
         <v>33</v>
       </c>
       <c r="C111" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D111" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E111" t="n">
         <v>30</v>
@@ -2322,10 +2322,10 @@
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C112" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D112" t="n">
         <v>53</v>
@@ -2342,13 +2342,13 @@
         <v>47</v>
       </c>
       <c r="C113" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D113" t="n">
         <v>51</v>
       </c>
       <c r="E113" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="114">
@@ -2356,13 +2356,13 @@
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C114" t="n">
         <v>53</v>
       </c>
       <c r="D114" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E114" t="n">
         <v>38</v>
@@ -2382,7 +2382,7 @@
         <v>42</v>
       </c>
       <c r="E115" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116">
@@ -2390,16 +2390,16 @@
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C116" t="n">
         <v>37</v>
       </c>
       <c r="D116" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E116" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117">
@@ -2407,10 +2407,10 @@
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C117" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D117" t="n">
         <v>53</v>
@@ -2430,10 +2430,10 @@
         <v>44</v>
       </c>
       <c r="D118" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E118" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="119">
@@ -2441,13 +2441,13 @@
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C119" t="n">
         <v>41</v>
       </c>
       <c r="D119" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E119" t="n">
         <v>33</v>
@@ -2458,13 +2458,13 @@
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C120" t="n">
         <v>58</v>
       </c>
       <c r="D120" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E120" t="n">
         <v>40</v>
@@ -2475,13 +2475,13 @@
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C121" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D121" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E121" t="n">
         <v>29</v>
@@ -2492,16 +2492,16 @@
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C122" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D122" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E122" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123">
@@ -2509,7 +2509,7 @@
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C123" t="n">
         <v>39</v>
@@ -2526,16 +2526,33 @@
         <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C124" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D124" t="n">
         <v>42</v>
       </c>
       <c r="E124" t="n">
         <v>35</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B125" t="n">
+        <v>31</v>
+      </c>
+      <c r="C125" t="n">
+        <v>23</v>
+      </c>
+      <c r="D125" t="n">
+        <v>29</v>
+      </c>
+      <c r="E125" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/nelly_trends_monthly.xlsx
+++ b/data/nelly_trends_monthly.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>42400</v>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>42429</v>
       </c>
       <c r="B3" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D3" t="n">
         <v>78</v>
-      </c>
-      <c r="C3" t="n">
-        <v>51</v>
-      </c>
-      <c r="D3" t="n">
-        <v>79</v>
       </c>
       <c r="E3" t="n">
         <v>85</v>
@@ -486,10 +486,10 @@
         <v>42460</v>
       </c>
       <c r="B4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" t="n">
         <v>83</v>
@@ -503,16 +503,16 @@
         <v>42490</v>
       </c>
       <c r="B5" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -523,10 +523,10 @@
         <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
@@ -537,16 +537,16 @@
         <v>42551</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -554,16 +554,16 @@
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
         <v>53</v>
       </c>
       <c r="D8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -571,13 +571,13 @@
         <v>42613</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
         <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
         <v>70</v>
@@ -591,13 +591,13 @@
         <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -605,13 +605,13 @@
         <v>42674</v>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" t="n">
         <v>82</v>
@@ -622,13 +622,13 @@
         <v>42704</v>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C12" t="n">
         <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12" t="n">
         <v>98</v>
@@ -639,16 +639,16 @@
         <v>42735</v>
       </c>
       <c r="B13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C13" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
@@ -656,16 +656,16 @@
         <v>42766</v>
       </c>
       <c r="B14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
@@ -673,16 +673,16 @@
         <v>42794</v>
       </c>
       <c r="B15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -690,13 +690,13 @@
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C16" t="n">
         <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
         <v>75</v>
@@ -707,13 +707,13 @@
         <v>42855</v>
       </c>
       <c r="B17" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" t="n">
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E17" t="n">
         <v>84</v>
@@ -727,13 +727,13 @@
         <v>98</v>
       </c>
       <c r="C18" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
         <v>75</v>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -741,13 +741,13 @@
         <v>42916</v>
       </c>
       <c r="B19" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" t="n">
         <v>71</v>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E19" t="n">
         <v>71</v>
@@ -758,16 +758,16 @@
         <v>42947</v>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>61</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
@@ -775,13 +775,13 @@
         <v>42978</v>
       </c>
       <c r="B21" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E21" t="n">
         <v>59</v>
@@ -798,7 +798,7 @@
         <v>64</v>
       </c>
       <c r="D22" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
         <v>71</v>
@@ -809,16 +809,16 @@
         <v>43039</v>
       </c>
       <c r="B23" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C23" t="n">
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
@@ -826,16 +826,16 @@
         <v>43069</v>
       </c>
       <c r="B24" t="n">
+        <v>90</v>
+      </c>
+      <c r="C24" t="n">
         <v>89</v>
       </c>
-      <c r="C24" t="n">
-        <v>81</v>
-      </c>
       <c r="D24" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
@@ -843,10 +843,10 @@
         <v>43100</v>
       </c>
       <c r="B25" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C25" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25" t="n">
         <v>87</v>
@@ -860,13 +860,13 @@
         <v>43131</v>
       </c>
       <c r="B26" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C26" t="n">
         <v>53</v>
       </c>
       <c r="D26" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E26" t="n">
         <v>65</v>
@@ -877,16 +877,16 @@
         <v>43159</v>
       </c>
       <c r="B27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C27" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E27" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28">
@@ -894,16 +894,16 @@
         <v>43190</v>
       </c>
       <c r="B28" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" t="n">
         <v>49</v>
       </c>
       <c r="D28" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E28" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -911,7 +911,7 @@
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C29" t="n">
         <v>61</v>
@@ -928,16 +928,16 @@
         <v>43251</v>
       </c>
       <c r="B30" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C30" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D30" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E30" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31">
@@ -945,10 +945,10 @@
         <v>43281</v>
       </c>
       <c r="B31" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D31" t="n">
         <v>91</v>
@@ -962,13 +962,13 @@
         <v>43312</v>
       </c>
       <c r="B32" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C32" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D32" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E32" t="n">
         <v>66</v>
@@ -979,16 +979,16 @@
         <v>43343</v>
       </c>
       <c r="B33" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C33" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
@@ -996,16 +996,16 @@
         <v>43373</v>
       </c>
       <c r="B34" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C34" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D34" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E34" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
@@ -1016,10 +1016,10 @@
         <v>67</v>
       </c>
       <c r="C35" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D35" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E35" t="n">
         <v>68</v>
@@ -1030,16 +1030,16 @@
         <v>43434</v>
       </c>
       <c r="B36" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C36" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D36" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E36" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37">
@@ -1050,10 +1050,10 @@
         <v>73</v>
       </c>
       <c r="C37" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D37" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E37" t="n">
         <v>59</v>
@@ -1064,16 +1064,16 @@
         <v>43496</v>
       </c>
       <c r="B38" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" t="n">
+        <v>60</v>
+      </c>
+      <c r="D38" t="n">
+        <v>77</v>
+      </c>
+      <c r="E38" t="n">
         <v>61</v>
-      </c>
-      <c r="D38" t="n">
-        <v>76</v>
-      </c>
-      <c r="E38" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="39">
@@ -1081,16 +1081,16 @@
         <v>43524</v>
       </c>
       <c r="B39" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C39" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D39" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E39" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
@@ -1098,7 +1098,7 @@
         <v>43555</v>
       </c>
       <c r="B40" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C40" t="n">
         <v>62</v>
@@ -1107,7 +1107,7 @@
         <v>76</v>
       </c>
       <c r="E40" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41">
@@ -1115,13 +1115,13 @@
         <v>43585</v>
       </c>
       <c r="B41" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C41" t="n">
         <v>60</v>
       </c>
       <c r="D41" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E41" t="n">
         <v>64</v>
@@ -1135,13 +1135,13 @@
         <v>86</v>
       </c>
       <c r="C42" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D42" t="n">
         <v>77</v>
       </c>
       <c r="E42" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43">
@@ -1149,13 +1149,13 @@
         <v>43646</v>
       </c>
       <c r="B43" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C43" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E43" t="n">
         <v>77</v>
@@ -1166,16 +1166,16 @@
         <v>43677</v>
       </c>
       <c r="B44" t="n">
+        <v>62</v>
+      </c>
+      <c r="C44" t="n">
         <v>61</v>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>60</v>
       </c>
-      <c r="D44" t="n">
-        <v>59</v>
-      </c>
       <c r="E44" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45">
@@ -1183,7 +1183,7 @@
         <v>43708</v>
       </c>
       <c r="B45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C45" t="n">
         <v>62</v>
@@ -1192,7 +1192,7 @@
         <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46">
@@ -1200,10 +1200,10 @@
         <v>43738</v>
       </c>
       <c r="B46" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D46" t="n">
         <v>64</v>
@@ -1217,16 +1217,16 @@
         <v>43769</v>
       </c>
       <c r="B47" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C47" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D47" t="n">
         <v>67</v>
       </c>
       <c r="E47" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48">
@@ -1234,16 +1234,16 @@
         <v>43799</v>
       </c>
       <c r="B48" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C48" t="n">
         <v>100</v>
       </c>
       <c r="D48" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E48" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49">
@@ -1251,13 +1251,13 @@
         <v>43830</v>
       </c>
       <c r="B49" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C49" t="n">
+        <v>76</v>
+      </c>
+      <c r="D49" t="n">
         <v>77</v>
-      </c>
-      <c r="D49" t="n">
-        <v>76</v>
       </c>
       <c r="E49" t="n">
         <v>58</v>
@@ -1268,16 +1268,16 @@
         <v>43861</v>
       </c>
       <c r="B50" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C50" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D50" t="n">
         <v>64</v>
       </c>
       <c r="E50" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51">
@@ -1285,16 +1285,16 @@
         <v>43890</v>
       </c>
       <c r="B51" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C51" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D51" t="n">
         <v>64</v>
       </c>
       <c r="E51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52">
@@ -1302,16 +1302,16 @@
         <v>43921</v>
       </c>
       <c r="B52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D52" t="n">
         <v>58</v>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53">
@@ -1319,16 +1319,16 @@
         <v>43951</v>
       </c>
       <c r="B53" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C53" t="n">
         <v>76</v>
       </c>
       <c r="D53" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E53" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54">
@@ -1336,10 +1336,10 @@
         <v>43982</v>
       </c>
       <c r="B54" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C54" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D54" t="n">
         <v>63</v>
@@ -1353,16 +1353,16 @@
         <v>44012</v>
       </c>
       <c r="B55" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C55" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D55" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E55" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56">
@@ -1373,7 +1373,7 @@
         <v>51</v>
       </c>
       <c r="C56" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D56" t="n">
         <v>44</v>
@@ -1390,13 +1390,13 @@
         <v>54</v>
       </c>
       <c r="C57" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D57" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58">
@@ -1404,10 +1404,10 @@
         <v>44104</v>
       </c>
       <c r="B58" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C58" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D58" t="n">
         <v>43</v>
@@ -1421,16 +1421,16 @@
         <v>44135</v>
       </c>
       <c r="B59" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C59" t="n">
         <v>63</v>
       </c>
       <c r="D59" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E59" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60">
@@ -1438,13 +1438,13 @@
         <v>44165</v>
       </c>
       <c r="B60" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C60" t="n">
         <v>76</v>
       </c>
       <c r="D60" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E60" t="n">
         <v>62</v>
@@ -1455,10 +1455,10 @@
         <v>44196</v>
       </c>
       <c r="B61" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C61" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D61" t="n">
         <v>47</v>
@@ -1472,13 +1472,13 @@
         <v>44227</v>
       </c>
       <c r="B62" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C62" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D62" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E62" t="n">
         <v>51</v>
@@ -1489,16 +1489,16 @@
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C63" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D63" t="n">
         <v>37</v>
       </c>
       <c r="E63" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
@@ -1506,7 +1506,7 @@
         <v>44286</v>
       </c>
       <c r="B64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C64" t="n">
         <v>50</v>
@@ -1523,10 +1523,10 @@
         <v>44316</v>
       </c>
       <c r="B65" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C65" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D65" t="n">
         <v>40</v>
@@ -1540,7 +1540,7 @@
         <v>44347</v>
       </c>
       <c r="B66" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C66" t="n">
         <v>53</v>
@@ -1549,7 +1549,7 @@
         <v>42</v>
       </c>
       <c r="E66" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67">
@@ -1557,7 +1557,7 @@
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C67" t="n">
         <v>57</v>
@@ -1566,7 +1566,7 @@
         <v>45</v>
       </c>
       <c r="E67" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68">
@@ -1574,16 +1574,16 @@
         <v>44408</v>
       </c>
       <c r="B68" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C68" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D68" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E68" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69">
@@ -1591,10 +1591,10 @@
         <v>44439</v>
       </c>
       <c r="B69" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C69" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D69" t="n">
         <v>38</v>
@@ -1608,16 +1608,16 @@
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C70" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D70" t="n">
         <v>36</v>
       </c>
       <c r="E70" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
@@ -1628,10 +1628,10 @@
         <v>46</v>
       </c>
       <c r="C71" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D71" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E71" t="n">
         <v>53</v>
@@ -1645,13 +1645,13 @@
         <v>59</v>
       </c>
       <c r="C72" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D72" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E72" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73">
@@ -1662,13 +1662,13 @@
         <v>55</v>
       </c>
       <c r="C73" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D73" t="n">
         <v>44</v>
       </c>
       <c r="E73" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74">
@@ -1679,7 +1679,7 @@
         <v>37</v>
       </c>
       <c r="C74" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D74" t="n">
         <v>32</v>
@@ -1710,7 +1710,7 @@
         <v>44651</v>
       </c>
       <c r="B76" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C76" t="n">
         <v>48</v>
@@ -1727,7 +1727,7 @@
         <v>44681</v>
       </c>
       <c r="B77" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C77" t="n">
         <v>53</v>
@@ -1736,7 +1736,7 @@
         <v>45</v>
       </c>
       <c r="E77" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78">
@@ -1744,16 +1744,16 @@
         <v>44712</v>
       </c>
       <c r="B78" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C78" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D78" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E78" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79">
@@ -1761,16 +1761,16 @@
         <v>44742</v>
       </c>
       <c r="B79" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C79" t="n">
         <v>51</v>
       </c>
       <c r="D79" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E79" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80">
@@ -1778,16 +1778,16 @@
         <v>44773</v>
       </c>
       <c r="B80" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C80" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D80" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E80" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81">
@@ -1798,7 +1798,7 @@
         <v>32</v>
       </c>
       <c r="C81" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D81" t="n">
         <v>28</v>
@@ -1812,16 +1812,16 @@
         <v>44834</v>
       </c>
       <c r="B82" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C82" t="n">
         <v>45</v>
       </c>
       <c r="D82" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E82" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83">
@@ -1829,13 +1829,13 @@
         <v>44865</v>
       </c>
       <c r="B83" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C83" t="n">
         <v>49</v>
       </c>
       <c r="D83" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E83" t="n">
         <v>46</v>
@@ -1852,10 +1852,10 @@
         <v>69</v>
       </c>
       <c r="D84" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E84" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85">
@@ -1863,10 +1863,10 @@
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C85" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D85" t="n">
         <v>40</v>
@@ -1880,16 +1880,16 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C86" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D86" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E86" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87">
@@ -1897,13 +1897,13 @@
         <v>44985</v>
       </c>
       <c r="B87" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C87" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D87" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E87" t="n">
         <v>38</v>
@@ -1914,13 +1914,13 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C88" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D88" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E88" t="n">
         <v>47</v>
@@ -1931,10 +1931,10 @@
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C89" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D89" t="n">
         <v>40</v>
@@ -1957,7 +1957,7 @@
         <v>32</v>
       </c>
       <c r="E90" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91">
@@ -1965,13 +1965,13 @@
         <v>45107</v>
       </c>
       <c r="B91" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C91" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D91" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E91" t="n">
         <v>39</v>
@@ -1982,10 +1982,10 @@
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D92" t="n">
         <v>24</v>
@@ -2002,13 +2002,13 @@
         <v>27</v>
       </c>
       <c r="C93" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D93" t="n">
         <v>24</v>
       </c>
       <c r="E93" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94">
@@ -2016,7 +2016,7 @@
         <v>45199</v>
       </c>
       <c r="B94" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C94" t="n">
         <v>33</v>
@@ -2033,10 +2033,10 @@
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C95" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D95" t="n">
         <v>34</v>
@@ -2050,13 +2050,13 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C96" t="n">
         <v>50</v>
       </c>
       <c r="D96" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E96" t="n">
         <v>31</v>
@@ -2067,13 +2067,13 @@
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C97" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D97" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E97" t="n">
         <v>24</v>
@@ -2084,10 +2084,10 @@
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C98" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D98" t="n">
         <v>33</v>
@@ -2101,10 +2101,10 @@
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C99" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D99" t="n">
         <v>31</v>
@@ -2118,7 +2118,7 @@
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C100" t="n">
         <v>36</v>
@@ -2135,13 +2135,13 @@
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C101" t="n">
         <v>38</v>
       </c>
       <c r="D101" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E101" t="n">
         <v>35</v>
@@ -2152,13 +2152,13 @@
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C102" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D102" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E102" t="n">
         <v>43</v>
@@ -2169,7 +2169,7 @@
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C103" t="n">
         <v>38</v>
@@ -2189,13 +2189,13 @@
         <v>27</v>
       </c>
       <c r="C104" t="n">
+        <v>33</v>
+      </c>
+      <c r="D104" t="n">
+        <v>27</v>
+      </c>
+      <c r="E104" t="n">
         <v>32</v>
-      </c>
-      <c r="D104" t="n">
-        <v>26</v>
-      </c>
-      <c r="E104" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="105">
@@ -2203,16 +2203,16 @@
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C105" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D105" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E105" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106">
@@ -2220,13 +2220,13 @@
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C106" t="n">
         <v>40</v>
       </c>
       <c r="D106" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E106" t="n">
         <v>29</v>
@@ -2237,16 +2237,16 @@
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C107" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D107" t="n">
         <v>53</v>
       </c>
       <c r="E107" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
@@ -2254,16 +2254,16 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C108" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D108" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E108" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109">
@@ -2271,13 +2271,13 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C109" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D109" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E109" t="n">
         <v>27</v>
@@ -2288,7 +2288,7 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C110" t="n">
         <v>45</v>
@@ -2308,10 +2308,10 @@
         <v>33</v>
       </c>
       <c r="C111" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D111" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E111" t="n">
         <v>30</v>
@@ -2322,16 +2322,16 @@
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C112" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D112" t="n">
         <v>53</v>
       </c>
       <c r="E112" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113">
@@ -2339,16 +2339,16 @@
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C113" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D113" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E113" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="114">
@@ -2356,7 +2356,7 @@
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C114" t="n">
         <v>53</v>
@@ -2365,7 +2365,7 @@
         <v>53</v>
       </c>
       <c r="E114" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="115">
@@ -2373,16 +2373,16 @@
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C115" t="n">
         <v>45</v>
       </c>
       <c r="D115" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E115" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116">
@@ -2393,10 +2393,10 @@
         <v>31</v>
       </c>
       <c r="C116" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D116" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E116" t="n">
         <v>34</v>
@@ -2407,13 +2407,13 @@
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C117" t="n">
         <v>53</v>
       </c>
       <c r="D117" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E117" t="n">
         <v>44</v>
@@ -2430,10 +2430,10 @@
         <v>44</v>
       </c>
       <c r="D118" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E118" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119">
@@ -2441,13 +2441,13 @@
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C119" t="n">
         <v>41</v>
       </c>
       <c r="D119" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E119" t="n">
         <v>33</v>
@@ -2458,16 +2458,16 @@
         <v>45991</v>
       </c>
       <c r="B120" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C120" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D120" t="n">
         <v>57</v>
       </c>
       <c r="E120" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121">
@@ -2475,16 +2475,16 @@
         <v>46022</v>
       </c>
       <c r="B121" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C121" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D121" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E121" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122">
@@ -2492,10 +2492,10 @@
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C122" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D122" t="n">
         <v>40</v>
@@ -2509,10 +2509,10 @@
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C123" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D123" t="n">
         <v>33</v>
@@ -2526,16 +2526,16 @@
         <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C124" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D124" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E124" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125">
@@ -2543,16 +2543,33 @@
         <v>46142</v>
       </c>
       <c r="B125" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C125" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D125" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E125" t="n">
-        <v>27</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B126" t="n">
+        <v>41</v>
+      </c>
+      <c r="C126" t="n">
+        <v>42</v>
+      </c>
+      <c r="D126" t="n">
+        <v>42</v>
+      </c>
+      <c r="E126" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
